--- a/Outputs/PtX_demand_SI.xlsx
+++ b/Outputs/PtX_demand_SI.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0001741233353551002</v>
-      </c>
+      <c r="C2" t="n">
+        <v>0.002584939845392091</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.002564464169028165</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0002591030566424013</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>2.492917080507675e-11</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5.216560135951444e-05</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,17 +522,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0001741233353551002</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2.492917080507675e-11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.216560135951444e-05</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,7 +557,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -570,7 +576,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -578,24 +584,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.0002387215930826525</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.670934892225633e-05</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>1.177742858439336e-05</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -603,14 +603,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.0002387215930826525</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0006702424723200279</v>
+        <v>4.670934892225633e-05</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>4.254209269224784e-05</v>
+        <v>1.177742858439336e-05</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -618,7 +620,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -627,17 +629,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0006702424723200279</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>4.254209269224784e-05</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -646,29 +652,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.003076450763477843</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6.343667119656581e-06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.820861712839786e-05</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.001980603565556</v>
-      </c>
-      <c r="J9" t="n">
-        <v>9.721874768721148e-05</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.0009813852249140999</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -678,28 +672,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.0310967063710098</v>
+        <v>0.003076450763477843</v>
       </c>
       <c r="G10" t="n">
-        <v>4.467658727433266e-05</v>
+        <v>6.343667119656581e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0006233899828972</v>
+        <v>6.820861712839786e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0126970711122363</v>
+        <v>0.001980603565556</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0005884652842813</v>
+        <v>9.721874768721148e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0096127645369281</v>
+        <v>0.0009813852249140999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -707,20 +701,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.001146085501813317</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.0310967063710098</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.467658727433266e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0006233899828972</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0126970711122363</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0005884652842813</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0096127645369281</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -729,7 +733,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0001710761505851674</v>
+        <v>0.001146085501813317</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -741,7 +745,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -750,83 +754,91 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.001555883245481137</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.03506423229108502</v>
-      </c>
-      <c r="G13" t="n">
-        <v>5.102025439398923e-05</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0006915986249547687</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.01478415980042846</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0006856840319685115</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.0105941497618422</v>
-      </c>
+        <v>0.00368817969301038</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0008407390440067625</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.0001710761505851674</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>2.086846941013904e-09</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7.967624283432319e-05</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.002584939845392091</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.002564464169028165</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.005503165995133919</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.03506423229108502</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.102025439398923e-05</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.0006915986249547687</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01478415980042846</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.0006856840319685115</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0105941497618422</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>0.002537569483705215</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.002608206666725712</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0002047132465682588</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -837,7 +849,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -847,12 +859,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>3.009997692457285e-10</v>
+        <v>0.0008407390440067625</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>2.086846941013904e-09</v>
+      </c>
       <c r="I17" t="n">
-        <v>2.634244282946768e-11</v>
+        <v>7.967624283432319e-05</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -860,7 +874,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -868,24 +882,18 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.0009450240860476342</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5.919770424781624e-05</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>1.816853598663156e-05</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -894,21 +902,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0003576098782463097</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>4.565330154468007e-05</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -917,17 +921,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>3.009997692457285e-10</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>2.634244282946768e-11</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -935,30 +943,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.0009450240860476342</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.001289817512211268</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.034122395044084e-05</v>
-      </c>
-      <c r="H21" t="n">
-        <v>8.303424373222285e-05</v>
-      </c>
+        <v>5.919770424781624e-05</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0013345459759956</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0001181049999963</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.0011103608962393</v>
-      </c>
+        <v>1.816853598663156e-05</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -968,28 +970,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.008290632842178699</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.802981521093037e-05</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0005877402693978</v>
-      </c>
+        <v>0.0003576098782463097</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0057965788066297</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0005222102927215999</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0093257754520696</v>
-      </c>
+        <v>4.565330154468007e-05</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -997,9 +991,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.001033086309782776</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1010,7 +1002,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1018,20 +1010,30 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.0006637443704830346</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.001289817512211268</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.034122395044084e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8.303424373222285e-05</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0013345459759956</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0001181049999963</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0011103608962393</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1039,65 +1041,61 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>0.002641854766313445</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.01083799728189062</v>
+        <v>0.008290632842178699</v>
       </c>
       <c r="G25" t="n">
-        <v>5.83710391613712e-05</v>
+        <v>4.802981521093037e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0006707765999769638</v>
+        <v>0.0005877402693978</v>
       </c>
       <c r="I25" t="n">
-        <v>0.007274622889333377</v>
+        <v>0.0057965788066297</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0006403152927179</v>
+        <v>0.0005222102927215999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0104361363483089</v>
+        <v>0.0093257754520696</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.001164232960626631</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.001033086309782776</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>3.537037472848137e-09</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0001279005782339543</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.002413152684796004</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1108,15 +1106,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.0006637443704830346</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1127,55 +1127,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.002537569483705215</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.002608206666725712</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.005259720697677708</v>
+      </c>
       <c r="F29" t="n">
-        <v>2.227370036129704e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.01083799728189062</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.83710391613712e-05</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0006707765999769638</v>
+      </c>
       <c r="I29" t="n">
-        <v>7.98862568146151e-10</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.007274622889333377</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0006403152927179</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0104361363483089</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>0.002499251978777664</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.002643589621623722</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.002485100133043488</v>
-      </c>
-      <c r="F30" t="n">
-        <v>9.349840352134126e-06</v>
-      </c>
+        <v>0.000160717766244496</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>5.066201414880919e-06</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1185,12 +1199,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>1.915507313125229e-05</v>
+        <v>0.001164232960626631</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>3.537037472848137e-09</v>
+      </c>
       <c r="I31" t="n">
-        <v>1.624687691858186e-05</v>
+        <v>0.0001279005782339543</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1198,7 +1214,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1207,29 +1223,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>7.203956199715926e-12</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.808113841955441e-13</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.199083786398123e-12</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.124473067637537e-11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>8.088805598649355e-13</v>
-      </c>
-      <c r="K32" t="n">
-        <v>7.597388414361179e-11</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1238,29 +1242,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.0001165720561071835</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.847795157599896e-05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0001087569693328</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0003461973294988</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0001519017325245</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0015818679863456</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1270,28 +1262,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0004604453049551258</v>
-      </c>
-      <c r="G34" t="n">
-        <v>4.332085924059987e-05</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0005330047601981</v>
-      </c>
+        <v>2.227370036129704e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0010193311062008</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0004494929781736</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.008694192101945299</v>
-      </c>
+        <v>7.98862568146151e-10</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1300,19 +1284,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.001163819040461</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.002485100133043488</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.349840352134126e-06</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>5.066201414880919e-06</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1320,20 +1308,22 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.001728885613091632</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1.915507313125229e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>1.624687691858186e-05</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1341,25 +1331,183 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>0.005377804786596121</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>7.203956199715926e-12</v>
+      </c>
+      <c r="G37" t="n">
+        <v>3.808113841955441e-13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.199083786398123e-12</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.124473067637537e-11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>8.088805598649355e-13</v>
+      </c>
+      <c r="K37" t="n">
+        <v>7.597388414361179e-11</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.0001165720561071835</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.847795157599896e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0001087569693328</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0003461973294988</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0001519017325245</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0015818679863456</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0004604453049551258</v>
+      </c>
+      <c r="G39" t="n">
+        <v>4.332085924059987e-05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0005330047601981</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0010193311062008</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0004494929781736</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.008694192101945299</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.001163819040461</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.001728885613091632</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.002499251978777664</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.002643589621623722</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.005538522552840617</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.001769757469746319</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>6.179881119741021e-05</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.0006417652697674566</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.001514742912374316</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.0006013947115069806</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.01027606016426478</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_SI.xlsx
+++ b/Outputs/PtX_demand_SI.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.0002591030566424013</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.003867550949853634</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0002568735268459</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0008564715863256</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0008810105960647</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -724,7 +732,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -733,7 +741,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.001146085501813317</v>
+        <v>0.00368817969301038</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -745,7 +753,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -754,7 +762,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.00368817969301038</v>
+        <v>0.001146085501813317</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -803,19 +811,19 @@
         <v>0.005503165995133919</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03506423229108502</v>
+        <v>0.03893178324093866</v>
       </c>
       <c r="G15" t="n">
-        <v>5.102025439398923e-05</v>
+        <v>0.0003078937812398892</v>
       </c>
       <c r="H15" t="n">
         <v>0.0006915986249547687</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01478415980042846</v>
+        <v>0.01564063138675406</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0006856840319685115</v>
+        <v>0.001566694628033211</v>
       </c>
       <c r="K15" t="n">
         <v>0.0105941497618422</v>
@@ -839,11 +847,19 @@
       <c r="E16" t="n">
         <v>0.0002047132465682588</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.0109665996836283</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0003014647768924</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0031276185176228</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0008688811834959</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1064,7 +1080,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1073,7 +1089,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.001033086309782776</v>
+        <v>0.002413152684796004</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1085,7 +1101,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1094,7 +1110,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.002413152684796004</v>
+        <v>0.001033086309782776</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1140,22 +1156,22 @@
         <v>0.002608206666725712</v>
       </c>
       <c r="E29" t="n">
-        <v>0.005259720697677708</v>
+        <v>0.005259720697677707</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01083799728189062</v>
+        <v>0.02180459696551892</v>
       </c>
       <c r="G29" t="n">
-        <v>5.83710391613712e-05</v>
+        <v>0.0003598358160537712</v>
       </c>
       <c r="H29" t="n">
         <v>0.0006707765999769638</v>
       </c>
       <c r="I29" t="n">
-        <v>0.007274622889333377</v>
+        <v>0.01040224140695618</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0006403152927179</v>
+        <v>0.0015091964762138</v>
       </c>
       <c r="K29" t="n">
         <v>0.0104361363483089</v>
@@ -1179,11 +1195,19 @@
       <c r="E30" t="n">
         <v>0.000160717766244496</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.01274141038284894</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0003385431825371</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0047808689103901</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0008874092585982</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1416,7 +1440,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1424,9 +1448,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.001163819040461</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1437,7 +1459,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1445,7 +1467,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.001163819040461</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1490,22 +1514,22 @@
         <v>0.002643589621623722</v>
       </c>
       <c r="E43" t="n">
-        <v>0.005538522552840617</v>
+        <v>0.005538522552840616</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001769757469746319</v>
+        <v>0.01451116785259525</v>
       </c>
       <c r="G43" t="n">
-        <v>6.179881119741021e-05</v>
+        <v>0.0004003419937345102</v>
       </c>
       <c r="H43" t="n">
         <v>0.0006417652697674566</v>
       </c>
       <c r="I43" t="n">
-        <v>0.001514742912374316</v>
+        <v>0.006295611822764415</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0006013947115069806</v>
+        <v>0.001488803970105181</v>
       </c>
       <c r="K43" t="n">
         <v>0.01027606016426478</v>
